--- a/booking_forms/018_crew_accommodation_booking_form--booking_forms.xlsx
+++ b/booking_forms/018_crew_accommodation_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'option-1',_'label':_'option-1'}</t>
+          <t>option-1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'option-1', 'label': 'option-1'}</t>
+          <t>option-1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'option-2',_'label':_'option-2'}</t>
+          <t>option-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'option-2', 'label': 'option-2'}</t>
+          <t>option-2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'option-3',_'label':_'option-3'}</t>
+          <t>option-3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'option-3', 'label': 'option-3'}</t>
+          <t>option-3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'option-4',_'label':_'option-4'}</t>
+          <t>option-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'option-4', 'label': 'option-4'}</t>
+          <t>option-4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'option-5',_'label':_'option-5'}</t>
+          <t>option-5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'option-5', 'label': 'option-5'}</t>
+          <t>option-5</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'option-6',_'label':_'option-6'}</t>
+          <t>option-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'option-6', 'label': 'option-6'}</t>
+          <t>option-6</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'option-7',_'label':_'option-7'}</t>
+          <t>option-7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'option-7', 'label': 'option-7'}</t>
+          <t>option-7</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'option-8',_'label':_'option-8'}</t>
+          <t>option-8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'option-8', 'label': 'option-8'}</t>
+          <t>option-8</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'option-9',_'label':_'option-9'}</t>
+          <t>option-9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'option-9', 'label': 'option-9'}</t>
+          <t>option-9</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'option-10',_'label':_'option-10'}</t>
+          <t>option-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'option-10', 'label': 'option-10'}</t>
+          <t>option-10</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'option-11',_'label':_'option-11'}</t>
+          <t>option-11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'option-11', 'label': 'option-11'}</t>
+          <t>option-11</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'option-12',_'label':_'option-12'}</t>
+          <t>option-12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'option-12', 'label': 'option-12'}</t>
+          <t>option-12</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'option-13',_'label':_'option-13'}</t>
+          <t>option-13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'option-13', 'label': 'option-13'}</t>
+          <t>option-13</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'option-14',_'label':_'option-14'}</t>
+          <t>option-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'option-14', 'label': 'option-14'}</t>
+          <t>option-14</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'option-15',_'label':_'option-15'}</t>
+          <t>option-15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'option-15', 'label': 'option-15'}</t>
+          <t>option-15</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'option-16',_'label':_'option-16'}</t>
+          <t>option-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'option-16', 'label': 'option-16'}</t>
+          <t>option-16</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'option-17',_'label':_'option-17'}</t>
+          <t>option-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'option-17', 'label': 'option-17'}</t>
+          <t>option-17</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'option-18',_'label':_'option-18'}</t>
+          <t>option-18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'option-18', 'label': 'option-18'}</t>
+          <t>option-18</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'option-19',_'label':_'option-19'}</t>
+          <t>option-19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'option-19', 'label': 'option-19'}</t>
+          <t>option-19</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'option-20',_'label':_'option-20'}</t>
+          <t>option-20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'option-20', 'label': 'option-20'}</t>
+          <t>option-20</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'option-21',_'label':_'option-21'}</t>
+          <t>option-21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'option-21', 'label': 'option-21'}</t>
+          <t>option-21</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'option-22',_'label':_'option-22'}</t>
+          <t>option-22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'option-22', 'label': 'option-22'}</t>
+          <t>option-22</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'option-23',_'label':_'option-23'}</t>
+          <t>option-23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'option-23', 'label': 'option-23'}</t>
+          <t>option-23</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'option-24',_'label':_'option-24'}</t>
+          <t>option-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'option-24', 'label': 'option-24'}</t>
+          <t>option-24</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'option-25',_'label':_'option-25'}</t>
+          <t>option-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'option-25', 'label': 'option-25'}</t>
+          <t>option-25</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'option-26',_'label':_'option-26'}</t>
+          <t>option-26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'option-26', 'label': 'option-26'}</t>
+          <t>option-26</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_'option-27',_'label':_'option-27'}</t>
+          <t>option-27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 'option-27', 'label': 'option-27'}</t>
+          <t>option-27</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_'option-28',_'label':_'option-28'}</t>
+          <t>option-28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 'option-28', 'label': 'option-28'}</t>
+          <t>option-28</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_'option-29',_'label':_'option-29'}</t>
+          <t>option-29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 'option-29', 'label': 'option-29'}</t>
+          <t>option-29</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'name':_'option-30',_'label':_'option-30'}</t>
+          <t>option-30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'name': 'option-30', 'label': 'option-30'}</t>
+          <t>option-30</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_'option-31',_'label':_'option-31'}</t>
+          <t>option-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': 'option-31', 'label': 'option-31'}</t>
+          <t>option-31</t>
         </is>
       </c>
     </row>
